--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -855,7 +855,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
+++ b/2-multi-document-abbyy-vs-tiled3x2+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.22250/oocihm.22250.139.xlsx
@@ -422,8 +422,8 @@
     <col width="39" customWidth="1" min="1" max="1"/>
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
-    <col width="33" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="27" customWidth="1" min="8" max="8"/>
@@ -431,9 +431,9 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
-    <col width="41" customWidth="1" min="14" max="14"/>
-    <col width="41" customWidth="1" min="15" max="15"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="14" max="14"/>
+    <col width="60" customWidth="1" min="15" max="15"/>
     <col width="31" customWidth="1" min="16" max="16"/>
     <col width="60" customWidth="1" min="17" max="17"/>
     <col width="30" customWidth="1" min="18" max="18"/>
@@ -597,16 +597,20 @@
       <c r="I2" s="1" t="inlineStr"/>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L23: stray/suspicious non-ASCII glyph(s): U+00B1 PLUS-MINUS SIGN :: é±¼</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+9C7C CJK UNIFIED IDEOGRAPH-9C7C | isolated marker/symbol line :: 鱼</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L54: stray/suspicious non-ASCII glyph(s): U+00AC NOT SIGN :: agreement,â‚¬</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L18: isolated marker/symbol line :: 0.</t>
@@ -614,7 +618,7 @@
       </c>
       <c r="O2" s="1" t="inlineStr">
         <is>
-          <t>L126: isolated marker/symbol line :: 7.</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE | symbol-only separator/garbage line :: [BOM]132</t>
         </is>
       </c>
       <c r="P2" s="1" t="inlineStr"/>
@@ -653,7 +657,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>130</t>
+          <t>98</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr"/>
@@ -664,12 +668,12 @@
       <c r="I3" s="1" t="inlineStr"/>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L46: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€œmore deta</t>
+          <t>L123: stray/suspicious non-ASCII glyph(s): U+FF1B FULLWIDTH SEMICOLON :: judgments； to the end, therefore,</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L59: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: sum of Â£â€”</t>
+          <t>L54: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: agreement,€</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -679,7 +683,11 @@
           <t>L22: isolated marker/symbol line :: 132</t>
         </is>
       </c>
-      <c r="O3" s="1" t="inlineStr"/>
+      <c r="O3" s="1" t="inlineStr">
+        <is>
+          <t>L126: isolated marker/symbol line :: 7.</t>
+        </is>
+      </c>
       <c r="P3" s="1" t="inlineStr"/>
       <c r="Q3" s="1" t="inlineStr">
         <is>
@@ -687,7 +695,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The character of the plaintiff must be described, without detail-</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
@@ -721,28 +733,24 @@
       <c r="G4" s="1" t="inlineStr"/>
       <c r="H4" s="1" t="inlineStr"/>
       <c r="I4" s="1" t="inlineStr"/>
-      <c r="J4" s="1" t="inlineStr">
-        <is>
-          <t>L100: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: r named, for the sum of Â£â€”, in an</t>
-        </is>
-      </c>
+      <c r="J4" s="1" t="inlineStr"/>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------term, in the year ----------(or G. H. late of</t>
+          <t>L121: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • The character of the plaintiff must be described, without detail-</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
       <c r="M4" s="1" t="inlineStr"/>
       <c r="N4" s="1" t="inlineStr">
         <is>
-          <t>L42: isolated marker/symbol line :: L</t>
+          <t>L23: stray/suspicious non-ASCII glyph(s): U+9C7C CJK UNIFIED IDEOGRAPH-9C7C | isolated marker/symbol line :: 鱼</t>
         </is>
       </c>
       <c r="O4" s="1" t="inlineStr"/>
       <c r="P4" s="1" t="inlineStr"/>
       <c r="Q4" s="1" t="inlineStr">
         <is>
-          <t>L97: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | punctuation artifact: double/multiple hyphen :: â€” --------term, in the year ----------(or G. H. late of</t>
+          <t>L97: punctuation artifact: double/multiple hyphen :: — --------term, in the year ----------(or G. H. late of</t>
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
@@ -762,7 +770,7 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
@@ -776,21 +784,13 @@
       <c r="G5" s="1" t="inlineStr"/>
       <c r="H5" s="1" t="inlineStr"/>
       <c r="I5" s="1" t="inlineStr"/>
-      <c r="J5" s="1" t="inlineStr">
-        <is>
-          <t>L129: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: â€”, on the-</t>
-        </is>
-      </c>
-      <c r="K5" s="1" t="inlineStr">
-        <is>
-          <t>L121: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ The character of the plaintiff must be described, without detail-</t>
-        </is>
-      </c>
+      <c r="J5" s="1" t="inlineStr"/>
+      <c r="K5" s="1" t="inlineStr"/>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L76: isolated marker/symbol line :: 7.</t>
+          <t>L42: isolated marker/symbol line :: L</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr"/>
@@ -835,7 +835,11 @@
       <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
-      <c r="N6" s="1" t="inlineStr"/>
+      <c r="N6" s="1" t="inlineStr">
+        <is>
+          <t>L76: isolated marker/symbol line :: 7.</t>
+        </is>
+      </c>
       <c r="O6" s="1" t="inlineStr"/>
       <c r="P6" s="1" t="inlineStr"/>
       <c r="Q6" s="1" t="inlineStr">
@@ -883,7 +887,7 @@
       <c r="P7" s="1" t="inlineStr"/>
       <c r="Q7" s="1" t="inlineStr">
         <is>
-          <t>L106: punctuation artifact: double/multiple hyphen :: defendant hereinafter named, for the sum of Â£----, in an</t>
+          <t>L106: punctuation artifact: double/multiple hyphen :: defendant hereinafter named, for the sum of £----, in an</t>
         </is>
       </c>
       <c r="R7" s="1" t="inlineStr"/>
@@ -989,12 +993,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1033,7 +1037,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1067,12 +1071,12 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D12" s="1" t="inlineStr"/>
@@ -1150,7 +1154,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
